--- a/financial/UNLID_財務モデル_v4.8.xlsx
+++ b/financial/UNLID_財務モデル_v4.8.xlsx
@@ -921,14 +921,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>UNLID 財務モデル 前提条件 v4.8  ─  単位：万円  |  中央値シナリオ</t>
+          <t>UNLID 財務モデル 前提条件 v5.0  ─  単位：万円  |  中央値シナリオ</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>v4.8変更：ベースシナリオシートを追加（期中平均HC適用・保守モデルとの比較）</t>
+          <t>v5.0変更：プロジェクト型定義刷新（タイプA限定・外注費35万/件明示）、収益源②③入替（②プロジェクト型・③人材紹介フィー）、Year2人材紹介を10件に修正</t>
         </is>
       </c>
     </row>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>40</v>
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1249,17 +1249,17 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>外注エンジニア費（プロジェクト分・万円）</t>
+          <t>プロジェクト型外注費（技術フリーランス協業費 35万/件・万円）</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>200</v>
+        <v>560</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>600</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="25">
@@ -3420,7 +3420,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>UNLID 損益計算書（P/L）v4.8  ─  単位：万円  |  前提条件シート連動</t>
+          <t>UNLID 損益計算書（P/L）v5.0  ─  単位：万円  |  前提条件シート連動</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  B2B受託収益</t>
+          <t xml:space="preserve">  ①B2B受託収益</t>
         </is>
       </c>
       <c r="B6" s="6">
@@ -3495,19 +3495,19 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  人材紹介フィー</t>
+          <t xml:space="preserve">  ②プロジェクト収益</t>
         </is>
       </c>
       <c r="B7" s="6">
-        <f>前提条件!B11</f>
+        <f>前提条件!B14</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>前提条件!C11</f>
+        <f>前提条件!C14</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>前提条件!D11</f>
+        <f>前提条件!D14</f>
         <v/>
       </c>
       <c r="E7" s="6">
@@ -3518,19 +3518,19 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  プロジェクト収益</t>
+          <t xml:space="preserve">  ③人材紹介フィー</t>
         </is>
       </c>
       <c r="B8" s="6">
-        <f>前提条件!B14</f>
+        <f>前提条件!B11</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>前提条件!C14</f>
+        <f>前提条件!C11</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>前提条件!D14</f>
+        <f>前提条件!D11</f>
         <v/>
       </c>
       <c r="E8" s="6">
@@ -3621,7 +3621,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  外注エンジニア費</t>
+          <t xml:space="preserve">  ②プロジェクト型外注費</t>
         </is>
       </c>
       <c r="B13" s="6">
@@ -8893,7 +8893,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="59" t="inlineStr">
         <is>
-          <t>UNLID ベースシナリオ比較 v4.8  ─  期中平均ヘッドカウント適用  |  超保守モデルとの比較</t>
+          <t>UNLID ベースシナリオ比較 v5.0  ─  期中平均ヘッドカウント適用  |  超保守モデルとの比較</t>
         </is>
       </c>
     </row>
